--- a/data/Basic Functions and Conditional formatting task.xlsx
+++ b/data/Basic Functions and Conditional formatting task.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\IOTB\Assignments\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6A7EB2-1B2E-46AE-B468-350F550E9DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Yearly Sales Report</t>
   </si>
@@ -108,12 +100,24 @@
   </si>
   <si>
     <t>Sum of Sales by Years</t>
+  </si>
+  <si>
+    <t>Tola is the most active salesrep</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Sum Total</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -201,7 +205,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -465,12 +469,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -498,18 +511,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -528,12 +532,49 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -842,23 +883,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="15.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="25" x14ac:dyDescent="0.5">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
@@ -901,11 +950,11 @@
         <v>16720</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="36"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="35"/>
       <c r="N3" s="7"/>
       <c r="O3" s="8" t="s">
         <v>9</v>
@@ -947,13 +996,16 @@
       <c r="K4" s="23">
         <v>2012</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="30" t="s">
         <v>12</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="14"/>
+      <c r="P4" s="14">
+        <f>COUNTIF(D3:D26, "Abdul")</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -978,14 +1030,26 @@
       <c r="H5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="N5" s="32"/>
+      <c r="I5" s="25">
+        <f>SUMIF(D3:D11, "Abdul", F3:F11)</f>
+        <v>12320</v>
+      </c>
+      <c r="J5" s="25">
+        <f>SUMIF(D12:D17, "Abdul", F12:F17)</f>
+        <v>23100</v>
+      </c>
+      <c r="K5" s="25">
+        <f>SUMIF(D18:D26, "Abdul", F18:F26)</f>
+        <v>25520</v>
+      </c>
+      <c r="N5" s="31"/>
       <c r="O5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="14"/>
+      <c r="P5" s="14">
+        <f>COUNTIF(D3:D26, "Ayo")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -1010,14 +1074,26 @@
       <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="N6" s="32"/>
+      <c r="I6" s="25">
+        <f>SUMIF(D3:D11, "Ayo", F3:F11)</f>
+        <v>16720</v>
+      </c>
+      <c r="J6" s="25">
+        <f>SUMIF(D12:D17, "Ayo", F12:F17)</f>
+        <v>6160</v>
+      </c>
+      <c r="K6" s="25">
+        <f>SUMIF(D18:D26, "Ayo", F18:F26)</f>
+        <v>7920</v>
+      </c>
+      <c r="N6" s="31"/>
       <c r="O6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="14"/>
+      <c r="P6" s="14">
+        <f>COUNTIF(D3:D26, "Ada")</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -1042,14 +1118,26 @@
       <c r="H7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="N7" s="32"/>
+      <c r="I7" s="25">
+        <f>SUMIF(D3:D11, "Ada", F3:F11)</f>
+        <v>26840</v>
+      </c>
+      <c r="J7" s="25">
+        <f>SUMIF(D12:D17, "Ada", F12:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>SUMIF(D18:D26, "Ada", F18:F26)</f>
+        <v>15840</v>
+      </c>
+      <c r="N7" s="31"/>
       <c r="O7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="14"/>
+      <c r="P7" s="14">
+        <f>COUNTIF(D3:D26, "Ese")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
@@ -1074,14 +1162,26 @@
       <c r="H8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="N8" s="33"/>
+      <c r="I8" s="25">
+        <f>SUMIF(D3:D11, "Ese", F3:F11)</f>
+        <v>19800</v>
+      </c>
+      <c r="J8" s="25">
+        <f>SUMIF(D12:D17, "Ese", F12:F17)</f>
+        <v>20900</v>
+      </c>
+      <c r="K8" s="25">
+        <f>SUMIF(D18:D26, "Ese", F18:F26)</f>
+        <v>11440</v>
+      </c>
+      <c r="N8" s="32"/>
       <c r="O8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="14"/>
+      <c r="P8" s="14">
+        <f>COUNTIF(D3:D26, "Tola")</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
@@ -1106,9 +1206,21 @@
       <c r="H9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
+      <c r="I9" s="25">
+        <f>SUMIF(D3:D11, "Tola", F3:F11)</f>
+        <v>29040</v>
+      </c>
+      <c r="J9" s="25">
+        <f>SUMIF(D12:D17, "Tola", F12:F17)</f>
+        <v>33440</v>
+      </c>
+      <c r="K9" s="25">
+        <f>SUMIF(D18:D26, "Tola", F18:F26)</f>
+        <v>20240</v>
+      </c>
+      <c r="N9" s="27" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1130,6 +1242,21 @@
       <c r="F10" s="4">
         <v>11000</v>
       </c>
+      <c r="H10" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="43">
+        <f>SUM(I5:I9)</f>
+        <v>104720</v>
+      </c>
+      <c r="J10" s="43">
+        <f t="shared" ref="J10:K10" si="1">SUM(J5:J9)</f>
+        <v>83600</v>
+      </c>
+      <c r="K10" s="43">
+        <f t="shared" si="1"/>
+        <v>80960</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1214,11 +1341,11 @@
       <c r="F14" s="4">
         <v>10560</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="39"/>
     </row>
     <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
@@ -1257,11 +1384,11 @@
       <c r="O15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S15" s="34" t="s">
+      <c r="S15" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="35"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -1286,16 +1413,28 @@
       <c r="H16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="16"/>
-      <c r="L16" s="31" t="s">
+      <c r="I16" s="13">
+        <f>SUM(E3:E26)</f>
+        <v>1224</v>
+      </c>
+      <c r="J16" s="16">
+        <f>SUM(F3:F26)</f>
+        <v>269280</v>
+      </c>
+      <c r="L16" s="30" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="N16" s="13">
+        <f>SUMIF(D3:D26, "Abdul", E3:E26)</f>
+        <v>277</v>
+      </c>
+      <c r="O16" s="13">
+        <f>SUMIF(D3:D26, "Abdul", F3:F26)</f>
+        <v>60940</v>
+      </c>
       <c r="R16" s="20" t="s">
         <v>4</v>
       </c>
@@ -1332,20 +1471,41 @@
       <c r="H17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="16"/>
-      <c r="L17" s="32"/>
+      <c r="I17" s="13">
+        <f>MIN(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J17" s="16">
+        <f>MIN(F3:F26)</f>
+        <v>5280</v>
+      </c>
+      <c r="L17" s="31"/>
       <c r="M17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="N17" s="13">
+        <f>SUMIF(D3:D26, "Ayo", E3:E26)</f>
+        <v>140</v>
+      </c>
+      <c r="O17" s="13">
+        <f>SUMIF(D3:D26, "Ayo", F3:F26)</f>
+        <v>30800</v>
+      </c>
       <c r="R17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
+      <c r="S17" s="25">
+        <f>SUMIF(D3:D11, "Abdul", E3:E11)</f>
+        <v>56</v>
+      </c>
+      <c r="T17" s="25">
+        <f>SUMIF(D12:D17, "Abdul", E12:E17)</f>
+        <v>105</v>
+      </c>
+      <c r="U17" s="25">
+        <f>SUMIF(D18:D26, "Abdul", E18:E26)</f>
+        <v>116</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -1370,20 +1530,41 @@
       <c r="H18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="16"/>
-      <c r="L18" s="32"/>
+      <c r="I18" s="13">
+        <f>MAX(E3:E26)</f>
+        <v>95</v>
+      </c>
+      <c r="J18" s="16">
+        <f>MAX(F3:F26)</f>
+        <v>20900</v>
+      </c>
+      <c r="L18" s="31"/>
       <c r="M18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="N18" s="13">
+        <f>SUMIF(D3:D26, "Ada", E3:E26)</f>
+        <v>194</v>
+      </c>
+      <c r="O18" s="13">
+        <f>SUMIF(D3:D26, "Ada", F3:F26)</f>
+        <v>42680</v>
+      </c>
       <c r="R18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
+      <c r="S18" s="25">
+        <f>SUMIF(D3:D11, "Ayo", E3:E11)</f>
+        <v>76</v>
+      </c>
+      <c r="T18" s="25">
+        <f>SUMIF(D12:D17, "Ayo", E12:E17)</f>
+        <v>28</v>
+      </c>
+      <c r="U18" s="25">
+        <f>SUMIF(D18:D26, "Ayo", E18:E26)</f>
+        <v>36</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
@@ -1408,20 +1589,41 @@
       <c r="H19" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="16"/>
-      <c r="L19" s="32"/>
+      <c r="I19" s="13">
+        <f>AVERAGE(E3:E26)</f>
+        <v>51</v>
+      </c>
+      <c r="J19" s="16">
+        <f>AVERAGE(F3:F26)</f>
+        <v>11220</v>
+      </c>
+      <c r="L19" s="31"/>
       <c r="M19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="N19" s="13">
+        <f>SUMIF(D3:D26, "Ese", E3:E26)</f>
+        <v>237</v>
+      </c>
+      <c r="O19" s="13">
+        <f>SUMIF(D3:D26, "Ese", F3:F26)</f>
+        <v>52140</v>
+      </c>
       <c r="R19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
+      <c r="S19" s="25">
+        <f>SUMIF(D3:D11, "Ada", E3:E11)</f>
+        <v>122</v>
+      </c>
+      <c r="T19" s="25">
+        <f>SUMIF(D12:D17, "Ada", E12:E17)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="25">
+        <f>SUMIF(D18:D26, "Ada", E18:E26)</f>
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
@@ -1446,20 +1648,41 @@
       <c r="H20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
-      <c r="L20" s="33"/>
+      <c r="I20" s="13">
+        <f>COUNT(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J20" s="14">
+        <f>COUNT(F3:F26)</f>
+        <v>24</v>
+      </c>
+      <c r="L20" s="32"/>
       <c r="M20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="N20" s="13">
+        <f>SUMIF(D3:D26, "Tola", E3:E26)</f>
+        <v>376</v>
+      </c>
+      <c r="O20" s="13">
+        <f>SUMIF(D3:D26, "Tola", F3:F26)</f>
+        <v>82720</v>
+      </c>
       <c r="R20" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
+      <c r="S20" s="25">
+        <f>SUMIF(D3:D11, "Ese", E3:E11)</f>
+        <v>90</v>
+      </c>
+      <c r="T20" s="25">
+        <f>SUMIF(D12:D17, "Ese", E12:E17)</f>
+        <v>95</v>
+      </c>
+      <c r="U20" s="25">
+        <f>SUMIF(D18:D26, "Ese", E18:E26)</f>
+        <v>52</v>
+      </c>
     </row>
     <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
@@ -1484,14 +1707,29 @@
       <c r="H21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="19"/>
+      <c r="I21" s="13">
+        <f>COUNTA(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J21" s="19">
+        <f>COUNTA(F3:F26)</f>
+        <v>24</v>
+      </c>
       <c r="R21" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
+      <c r="S21" s="25">
+        <f>SUMIF(D3:D11, "Tola", E3:E11)</f>
+        <v>132</v>
+      </c>
+      <c r="T21" s="25">
+        <f>SUMIF(D12:D17, "Tola", E12:E17)</f>
+        <v>152</v>
+      </c>
+      <c r="U21" s="25">
+        <f>SUMIF(D18:D26, "Tola", E18:E26)</f>
+        <v>92</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
@@ -1513,6 +1751,21 @@
       <c r="F22" s="4">
         <v>10340</v>
       </c>
+      <c r="R22" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="S22" s="43">
+        <f>SUM(S17:S21)</f>
+        <v>476</v>
+      </c>
+      <c r="T22" s="43">
+        <f t="shared" ref="T22:U22" si="2">SUM(T17:T21)</f>
+        <v>380</v>
+      </c>
+      <c r="U22" s="43">
+        <f t="shared" si="2"/>
+        <v>368</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
@@ -1534,6 +1787,13 @@
       <c r="F23" s="4">
         <v>9020</v>
       </c>
+      <c r="R23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="41">
+        <f>SUM(S22:U22)</f>
+        <v>1224</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
@@ -1555,6 +1815,20 @@
       <c r="F24" s="4">
         <v>11440</v>
       </c>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="28"/>
+      <c r="R24" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="S24" s="41">
+        <f>AVERAGE(S22:U22)</f>
+        <v>408</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
@@ -1576,6 +1850,12 @@
       <c r="F25" s="4">
         <v>7920</v>
       </c>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
@@ -1597,16 +1877,97 @@
       <c r="F26" s="4">
         <v>13200</v>
       </c>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+    </row>
+    <row r="33" spans="8:13" x14ac:dyDescent="0.35">
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="16">
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="L16:L20"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="N4:N8"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="L16:L20"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="H28:M28"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3:F26">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>6000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>15000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>